--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N91_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.057093135006496</v>
+        <v>0.9842776344385556</v>
       </c>
       <c r="D2" t="n">
-        <v>6.321372535497551</v>
+        <v>1.027223037018352</v>
       </c>
       <c r="E2" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F2" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.109676746743244</v>
+        <v>0.6678224713457772</v>
       </c>
       <c r="D3" t="n">
-        <v>3.955361565849314</v>
+        <v>0.6427462544505136</v>
       </c>
       <c r="E3" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F3" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.26287106624324</v>
+        <v>4.105216548264526</v>
       </c>
       <c r="D4" t="n">
-        <v>18.97134574184325</v>
+        <v>3.082843683049528</v>
       </c>
       <c r="E4" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F4" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.05392756376444</v>
+        <v>4.396263229111722</v>
       </c>
       <c r="D5" t="n">
-        <v>26.72545602978553</v>
+        <v>4.34288660484015</v>
       </c>
       <c r="E5" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F5" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.77413221778374</v>
+        <v>4.838296485389858</v>
       </c>
       <c r="D6" t="n">
-        <v>27.11698493988291</v>
+        <v>4.406510052730973</v>
       </c>
       <c r="E6" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F6" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.7688693293833</v>
+        <v>6.949941266024786</v>
       </c>
       <c r="D7" t="n">
-        <v>57.44858319518121</v>
+        <v>9.335394769216947</v>
       </c>
       <c r="E7" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F7" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.72975305530793</v>
+        <v>5.481084871487539</v>
       </c>
       <c r="D8" t="n">
-        <v>48.01107885513375</v>
+        <v>7.801800313959234</v>
       </c>
       <c r="E8" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F8" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.25801670885522</v>
+        <v>4.429427715188974</v>
       </c>
       <c r="D9" t="n">
-        <v>24.466521236262</v>
+        <v>3.975809700892576</v>
       </c>
       <c r="E9" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F9" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.58816778987068</v>
+        <v>7.083077265853986</v>
       </c>
       <c r="D10" t="n">
-        <v>57.11272024819954</v>
+        <v>9.280817040332424</v>
       </c>
       <c r="E10" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F10" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.85840031689227</v>
+        <v>7.451990051494994</v>
       </c>
       <c r="D11" t="n">
-        <v>62.61468175988682</v>
+        <v>10.17488578598161</v>
       </c>
       <c r="E11" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F11" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>6.865914305324324</v>
+        <v>1.115711074615203</v>
       </c>
       <c r="D12" t="n">
-        <v>41.55952268501446</v>
+        <v>6.753422436314851</v>
       </c>
       <c r="E12" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F12" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.01135777277262</v>
+        <v>1.789345638075551</v>
       </c>
       <c r="D13" t="n">
-        <v>46.62385914212825</v>
+        <v>7.576377110595842</v>
       </c>
       <c r="E13" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F13" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15.7003017455153</v>
+        <v>2.551299033646236</v>
       </c>
       <c r="D14" t="n">
-        <v>27.48809467297787</v>
+        <v>4.466815384358904</v>
       </c>
       <c r="E14" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F14" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.78062133585992</v>
+        <v>4.676850967077238</v>
       </c>
       <c r="D15" t="n">
-        <v>16.97626913540116</v>
+        <v>2.758643734502688</v>
       </c>
       <c r="E15" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F15" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>8.270985772008565</v>
+        <v>1.344035187951392</v>
       </c>
       <c r="D16" t="n">
-        <v>64.04912646984793</v>
+        <v>10.40798305135029</v>
       </c>
       <c r="E16" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F16" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>9.953466172435173</v>
+        <v>1.617438253020716</v>
       </c>
       <c r="D17" t="n">
-        <v>59.58847620109708</v>
+        <v>9.683127382678276</v>
       </c>
       <c r="E17" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F17" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>54.35441202148517</v>
+        <v>8.83259195349134</v>
       </c>
       <c r="D18" t="n">
-        <v>20.31898068870172</v>
+        <v>3.30183436191403</v>
       </c>
       <c r="E18" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F18" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>12.17748190577132</v>
+        <v>1.97884080968784</v>
       </c>
       <c r="D19" t="n">
-        <v>77.67872907001168</v>
+        <v>12.6227934738769</v>
       </c>
       <c r="E19" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F19" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>30.13747949663273</v>
+        <v>4.897340418202819</v>
       </c>
       <c r="D20" t="n">
-        <v>77.27515531902866</v>
+        <v>12.55721273934216</v>
       </c>
       <c r="E20" t="n">
-        <v>14.82540707231256</v>
+        <v>2.409128649250791</v>
       </c>
       <c r="F20" t="n">
-        <v>22.38720597295625</v>
+        <v>3.637920970605389</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
